--- a/config/bms/BAU_高特.xlsx
+++ b/config/bms/BAU_高特.xlsx
@@ -30396,7 +30396,7 @@
         <v>18</v>
       </c>
       <c r="H88" s="3">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>19</v>
